--- a/Data/Building/Corridor.Temperature.xlsx
+++ b/Data/Building/Corridor.Temperature.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H151"/>
+  <dimension ref="A1:I145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1709235925</v>
+        <v>1711829017</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -501,6 +506,7 @@
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -519,7 +525,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1709261615</v>
+        <v>1711853898</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -533,6 +539,7 @@
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -551,7 +558,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1709267993</v>
+        <v>1711859731</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -565,6 +572,7 @@
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -583,7 +591,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1709224743</v>
+        <v>1711911248</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -597,6 +605,7 @@
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -615,7 +624,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1709233032</v>
+        <v>1711920959</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -629,6 +638,7 @@
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -647,7 +657,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1709243156</v>
+        <v>1711932323</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -657,10 +667,11 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Corridor.Temperature.state: ExcessivelyCold</t>
+          <t>Corridor.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -679,7 +690,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1709259288</v>
+        <v>1711938273</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -689,10 +700,11 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Corridor.Temperature.state: Cold</t>
+          <t>Corridor.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -711,7 +723,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1709267027</v>
+        <v>1711993201</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -725,6 +737,7 @@
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -743,7 +756,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1709314388</v>
+        <v>1711999053</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -757,6 +770,7 @@
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -775,7 +789,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1709324925</v>
+        <v>1712008372</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -789,6 +803,11 @@
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -807,7 +826,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1709340404</v>
+        <v>1712022276</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -821,6 +840,7 @@
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -839,7 +859,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1709347062</v>
+        <v>1712030573</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -853,6 +873,7 @@
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -871,7 +892,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1709355758</v>
+        <v>1712079587</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -881,10 +902,11 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Corridor.Temperature.state: Warm</t>
+          <t>Corridor.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -903,7 +925,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1709364097</v>
+        <v>1712088839</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -913,10 +935,15 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Corridor.Temperature.state: Comfortable</t>
+          <t>Corridor.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -935,7 +962,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1709400994</v>
+        <v>1712106032</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -949,6 +976,7 @@
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -967,7 +995,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1709410332</v>
+        <v>1712113355</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -977,10 +1005,11 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Corridor.Temperature.state: ExcessivelyCold</t>
+          <t>Corridor.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -999,7 +1028,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1709426279</v>
+        <v>1712122924</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1009,10 +1038,11 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Corridor.Temperature.state: Cold</t>
+          <t>Corridor.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1031,7 +1061,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1709433688</v>
+        <v>1712132470</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1045,6 +1075,7 @@
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1063,7 +1094,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1709442537</v>
+        <v>1712166661</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1073,10 +1104,11 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Corridor.Temperature.state: Warm</t>
+          <t>Corridor.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1095,7 +1127,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1709448121</v>
+        <v>1712176302</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1105,10 +1137,15 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Corridor.Temperature.state: Comfortable</t>
+          <t>Corridor.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1127,7 +1164,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1709488593</v>
+        <v>1712190006</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1141,6 +1178,7 @@
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1159,7 +1197,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1709497863</v>
+        <v>1712197288</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1169,10 +1207,11 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Corridor.Temperature.state: ExcessivelyCold</t>
+          <t>Corridor.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1191,7 +1230,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1709515312</v>
+        <v>1712206948</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1201,10 +1240,11 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Corridor.Temperature.state: Cold</t>
+          <t>Corridor.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1223,7 +1263,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1709522819</v>
+        <v>1712215860</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1237,6 +1277,7 @@
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1255,7 +1296,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1709571889</v>
+        <v>1712254358</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1269,6 +1310,7 @@
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1287,7 +1329,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1709581074</v>
+        <v>1712263775</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1301,6 +1343,11 @@
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1319,7 +1366,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1709600311</v>
+        <v>1712278915</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1333,6 +1380,7 @@
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1351,7 +1399,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1709607560</v>
+        <v>1712286081</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1365,6 +1413,7 @@
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1383,7 +1432,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1709616560</v>
+        <v>1712338017</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1393,10 +1442,11 @@
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Corridor.Temperature.state: Warm</t>
+          <t>Corridor.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1415,7 +1465,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1709624846</v>
+        <v>1712347167</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1425,10 +1475,15 @@
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Corridor.Temperature.state: Comfortable</t>
+          <t>Corridor.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1447,7 +1502,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1709661277</v>
+        <v>1712367608</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1461,6 +1516,7 @@
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1479,7 +1535,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1709671348</v>
+        <v>1712374937</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1489,10 +1545,11 @@
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Corridor.Temperature.state: ExcessivelyCold</t>
+          <t>Corridor.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1511,7 +1568,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1709689678</v>
+        <v>1712384762</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1521,10 +1578,11 @@
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Corridor.Temperature.state: Cold</t>
+          <t>Corridor.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1543,7 +1601,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1709697437</v>
+        <v>1712398585</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1557,6 +1615,7 @@
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1575,7 +1634,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1709706867</v>
+        <v>1712425837</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1585,10 +1644,11 @@
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Corridor.Temperature.state: Warm</t>
+          <t>Corridor.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1607,7 +1667,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1709719179</v>
+        <v>1712435146</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1617,10 +1677,15 @@
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Corridor.Temperature.state: Comfortable</t>
+          <t>Corridor.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1639,7 +1704,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1709750218</v>
+        <v>1712455810</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1653,6 +1718,7 @@
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1671,7 +1737,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1709760395</v>
+        <v>1712463536</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1681,10 +1747,11 @@
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Corridor.Temperature.state: ExcessivelyCold</t>
+          <t>Corridor.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1703,7 +1770,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1709780277</v>
+        <v>1712472525</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1713,10 +1780,11 @@
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Corridor.Temperature.state: Cold</t>
+          <t>Corridor.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1735,7 +1803,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1709789755</v>
+        <v>1712485835</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1749,6 +1817,7 @@
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1767,7 +1836,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1709833285</v>
+        <v>1712512446</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1781,6 +1850,7 @@
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1799,7 +1869,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1709843329</v>
+        <v>1712521643</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1813,6 +1883,11 @@
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1831,7 +1906,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1709856724</v>
+        <v>1712538295</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1845,6 +1920,7 @@
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1863,7 +1939,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1709864529</v>
+        <v>1712546149</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1877,6 +1953,7 @@
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1895,7 +1972,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1709921348</v>
+        <v>1712600048</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1909,6 +1986,7 @@
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1927,7 +2005,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1709930670</v>
+        <v>1712609059</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1941,6 +2019,11 @@
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1959,7 +2042,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1709943182</v>
+        <v>1712624575</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1973,6 +2056,7 @@
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1991,7 +2075,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1709950389</v>
+        <v>1712630704</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2005,6 +2089,7 @@
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2023,7 +2108,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1709958771</v>
+        <v>1712637926</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2037,6 +2122,7 @@
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2055,7 +2141,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1709966642</v>
+        <v>1712645044</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2069,6 +2155,7 @@
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2087,7 +2174,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1710006797</v>
+        <v>1712686445</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2101,6 +2188,7 @@
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2119,7 +2207,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1710016519</v>
+        <v>1712697406</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2133,6 +2221,11 @@
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2151,7 +2244,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1710033503</v>
+        <v>1712715107</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2165,6 +2258,7 @@
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2183,7 +2277,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1710040566</v>
+        <v>1712723883</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2197,6 +2291,7 @@
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2215,7 +2310,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1710048608</v>
+        <v>1712770538</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2225,10 +2320,11 @@
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Corridor.Temperature.state: Warm</t>
+          <t>Corridor.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2247,7 +2343,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1710057092</v>
+        <v>1712779625</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2257,10 +2353,15 @@
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Corridor.Temperature.state: Comfortable</t>
+          <t>Corridor.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2279,7 +2380,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1710093248</v>
+        <v>1712798780</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2293,6 +2394,7 @@
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2311,7 +2413,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1710102717</v>
+        <v>1712805499</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2321,10 +2423,11 @@
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Corridor.Temperature.state: ExcessivelyCold</t>
+          <t>Corridor.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2343,7 +2446,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1710119466</v>
+        <v>1712860192</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2357,6 +2460,7 @@
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2375,7 +2479,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1710126797</v>
+        <v>1712869277</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2385,10 +2489,15 @@
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Corridor.Temperature.state: Comfortable</t>
+          <t>Corridor.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2407,7 +2516,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1710135298</v>
+        <v>1712883961</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2417,10 +2526,11 @@
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Corridor.Temperature.state: Warm</t>
+          <t>Corridor.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2439,7 +2549,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1710145095</v>
+        <v>1712890949</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2453,6 +2563,7 @@
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2471,7 +2582,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1710178939</v>
+        <v>1712947625</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2485,6 +2596,7 @@
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2503,7 +2615,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1710188570</v>
+        <v>1712957201</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2517,6 +2629,11 @@
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2535,7 +2652,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1710204873</v>
+        <v>1712971795</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2549,6 +2666,7 @@
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2567,7 +2685,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1710212212</v>
+        <v>1712979473</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2581,6 +2699,7 @@
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2599,7 +2718,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1710220901</v>
+        <v>1712989033</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2613,6 +2732,7 @@
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2631,7 +2751,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1710228444</v>
+        <v>1712999764</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2645,6 +2765,7 @@
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2663,7 +2784,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1710264343</v>
+        <v>1713030609</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2677,6 +2798,7 @@
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2695,7 +2817,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1710275712</v>
+        <v>1713039975</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2709,6 +2831,11 @@
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2727,7 +2854,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1710281241</v>
+        <v>1713059340</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -2741,6 +2868,7 @@
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2759,7 +2887,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1710300784</v>
+        <v>1713067231</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -2773,6 +2901,7 @@
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2791,7 +2920,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1710309819</v>
+        <v>1713077373</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -2805,6 +2934,7 @@
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2823,7 +2953,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1710323386</v>
+        <v>1713088525</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -2837,6 +2967,7 @@
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2855,7 +2986,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1710353603</v>
+        <v>1713118457</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -2869,6 +3000,7 @@
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2887,7 +3019,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1710362845</v>
+        <v>1713128065</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -2901,6 +3033,11 @@
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2919,7 +3056,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1710385739</v>
+        <v>1713143543</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -2933,6 +3070,7 @@
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2951,7 +3089,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1710394354</v>
+        <v>1713149927</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -2965,6 +3103,7 @@
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2983,7 +3122,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1710437711</v>
+        <v>1713202375</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -2997,6 +3136,7 @@
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3015,7 +3155,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1710446856</v>
+        <v>1713211902</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -3029,6 +3169,11 @@
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3047,7 +3192,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1710463513</v>
+        <v>1713226715</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3061,6 +3206,7 @@
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3079,7 +3225,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1710470250</v>
+        <v>1713233598</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -3093,6 +3239,7 @@
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3111,7 +3258,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1710527075</v>
+        <v>1713241412</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3121,10 +3268,11 @@
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Corridor.Temperature.state: Cold</t>
+          <t>Corridor.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3143,7 +3291,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1710540981</v>
+        <v>1713250128</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3153,10 +3301,11 @@
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Corridor.Temperature.state: ExcessivelyCold</t>
+          <t>Corridor.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3175,7 +3324,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1710545304</v>
+        <v>1713289804</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3189,6 +3338,7 @@
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3207,7 +3357,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1710555665</v>
+        <v>1713299248</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3217,10 +3367,15 @@
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Corridor.Temperature.state: Comfortable</t>
+          <t>Corridor.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3239,7 +3394,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1710615199</v>
+        <v>1713314390</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3253,6 +3408,7 @@
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3271,7 +3427,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1710624526</v>
+        <v>1713321319</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3281,10 +3437,11 @@
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Corridor.Temperature.state: ExcessivelyCold</t>
+          <t>Corridor.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3303,7 +3460,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1710638619</v>
+        <v>1713378985</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3317,6 +3474,7 @@
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3335,7 +3493,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1710645833</v>
+        <v>1713391125</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -3345,10 +3503,15 @@
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Corridor.Temperature.state: Comfortable</t>
+          <t>Corridor.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3367,7 +3530,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1710699591</v>
+        <v>1713395378</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3381,6 +3544,7 @@
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3399,7 +3563,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1710709740</v>
+        <v>1713409428</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3409,10 +3573,11 @@
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Corridor.Temperature.state: ExcessivelyCold</t>
+          <t>Corridor.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3431,7 +3596,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>1710722302</v>
+        <v>1713461259</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -3445,6 +3610,7 @@
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3463,7 +3629,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>1710729472</v>
+        <v>1713470310</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3473,10 +3639,15 @@
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Corridor.Temperature.state: Comfortable</t>
+          <t>Corridor.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3495,7 +3666,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1710785418</v>
+        <v>1713487936</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -3509,6 +3680,7 @@
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3527,7 +3699,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>1710794639</v>
+        <v>1713493871</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -3537,10 +3709,11 @@
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Corridor.Temperature.state: ExcessivelyCold</t>
+          <t>Corridor.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3559,7 +3732,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>1710810032</v>
+        <v>1713501692</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -3569,10 +3742,11 @@
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Corridor.Temperature.state: Cold</t>
+          <t>Corridor.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3591,7 +3765,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1710816913</v>
+        <v>1713542467</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3605,6 +3779,7 @@
         </is>
       </c>
       <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3623,7 +3798,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1710825170</v>
+        <v>1713549554</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -3633,10 +3808,11 @@
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Corridor.Temperature.state: Warm</t>
+          <t>Corridor.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3655,7 +3831,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>1710831583</v>
+        <v>1713559177</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -3665,10 +3841,15 @@
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Corridor.Temperature.state: Comfortable</t>
+          <t>Corridor.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3687,7 +3868,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1710866243</v>
+        <v>1713576472</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -3701,6 +3882,7 @@
         </is>
       </c>
       <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3719,7 +3901,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1710877335</v>
+        <v>1713583493</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -3729,10 +3911,11 @@
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Corridor.Temperature.state: ExcessivelyCold</t>
+          <t>Corridor.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3751,7 +3934,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>1710887219</v>
+        <v>1713592516</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -3761,10 +3944,11 @@
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Corridor.Temperature.state: Cold</t>
+          <t>Corridor.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3783,7 +3967,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1710895869</v>
+        <v>1713629237</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -3797,6 +3981,7 @@
         </is>
       </c>
       <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3815,7 +4000,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1710901088</v>
+        <v>1713635163</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -3825,10 +4010,11 @@
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Corridor.Temperature.state: Warm</t>
+          <t>Corridor.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3847,7 +4033,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>1710911483</v>
+        <v>1713644473</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -3857,10 +4043,15 @@
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Corridor.Temperature.state: ExcessivelyHot</t>
+          <t>Corridor.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3879,7 +4070,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>1710929253</v>
+        <v>1713662841</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -3889,10 +4080,11 @@
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Corridor.Temperature.state: Warm</t>
+          <t>Corridor.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3911,7 +4103,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1710957282</v>
+        <v>1713670276</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -3925,6 +4117,7 @@
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3943,7 +4136,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1710966904</v>
+        <v>1713718432</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -3957,6 +4150,7 @@
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3975,7 +4169,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>1710986528</v>
+        <v>1713727843</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -3985,10 +4179,15 @@
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Corridor.Temperature.state: Comfortable</t>
+          <t>Corridor.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4007,7 +4206,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>1710992853</v>
+        <v>1713746274</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -4017,10 +4216,11 @@
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Corridor.Temperature.state: Warm</t>
+          <t>Corridor.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4039,7 +4239,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>1711004333</v>
+        <v>1713752479</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -4049,10 +4249,11 @@
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Corridor.Temperature.state: ExcessivelyHot</t>
+          <t>Corridor.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4071,7 +4272,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1711016576</v>
+        <v>1713760239</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -4085,6 +4286,7 @@
         </is>
       </c>
       <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4103,7 +4305,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1711045633</v>
+        <v>1713769381</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -4117,6 +4319,7 @@
         </is>
       </c>
       <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4135,7 +4338,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1711055210</v>
+        <v>1713809464</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -4149,6 +4352,7 @@
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4167,7 +4371,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>1711074566</v>
+        <v>1713818578</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -4177,10 +4381,15 @@
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Corridor.Temperature.state: Comfortable</t>
+          <t>Corridor.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4199,7 +4408,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>1711082420</v>
+        <v>1713835977</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -4209,10 +4418,11 @@
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Corridor.Temperature.state: Warm</t>
+          <t>Corridor.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4231,7 +4441,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>1711128672</v>
+        <v>1713843906</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -4245,6 +4455,7 @@
         </is>
       </c>
       <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4263,7 +4474,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>1711137856</v>
+        <v>1713893546</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -4277,6 +4488,7 @@
         </is>
       </c>
       <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4295,7 +4507,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>1711155276</v>
+        <v>1713902705</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -4305,10 +4517,15 @@
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Corridor.Temperature.state: Comfortable</t>
+          <t>Corridor.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4327,7 +4544,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>1711163388</v>
+        <v>1713919587</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -4337,10 +4554,11 @@
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Corridor.Temperature.state: Warm</t>
+          <t>Corridor.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4359,7 +4577,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>1711219686</v>
+        <v>1713926878</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -4373,6 +4591,7 @@
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4391,7 +4610,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>1711229675</v>
+        <v>1713934433</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -4401,10 +4620,11 @@
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Corridor.Temperature.state: Cold</t>
+          <t>Corridor.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4423,7 +4643,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1711241258</v>
+        <v>1713943095</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -4437,6 +4657,7 @@
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4455,7 +4676,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>1711252625</v>
+        <v>1713982953</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -4465,10 +4686,11 @@
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Corridor.Temperature.state: Warm</t>
+          <t>Corridor.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4487,7 +4709,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>1711265528</v>
+        <v>1713992341</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -4497,10 +4719,15 @@
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Corridor.Temperature.state: Comfortable</t>
+          <t>Corridor.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4519,7 +4746,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>1711302662</v>
+        <v>1714004442</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -4533,6 +4760,7 @@
         </is>
       </c>
       <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4551,7 +4779,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>1711312324</v>
+        <v>1714011640</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -4561,10 +4789,11 @@
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Corridor.Temperature.state: ExcessivelyCold</t>
+          <t>Corridor.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4583,7 +4812,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>1711329516</v>
+        <v>1714069464</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -4597,6 +4826,7 @@
         </is>
       </c>
       <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4615,7 +4845,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>1711335677</v>
+        <v>1714079266</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -4625,10 +4855,15 @@
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Corridor.Temperature.state: Comfortable</t>
+          <t>Corridor.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4647,7 +4882,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>1711343350</v>
+        <v>1714090899</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -4657,10 +4892,11 @@
       <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Corridor.Temperature.state: Warm</t>
+          <t>Corridor.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4679,7 +4915,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>1711350440</v>
+        <v>1714095385</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -4693,6 +4929,7 @@
         </is>
       </c>
       <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4711,7 +4948,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>1711389002</v>
+        <v>1714109533</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -4725,6 +4962,7 @@
         </is>
       </c>
       <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4743,7 +4981,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>1711398649</v>
+        <v>1714160924</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -4757,6 +4995,11 @@
         </is>
       </c>
       <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4775,7 +5018,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>1711415026</v>
+        <v>1714181133</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -4789,6 +5032,7 @@
         </is>
       </c>
       <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4807,7 +5051,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>1711421864</v>
+        <v>1714188186</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -4821,6 +5065,7 @@
         </is>
       </c>
       <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4839,7 +5084,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>1711429147</v>
+        <v>1714197455</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -4853,6 +5098,7 @@
         </is>
       </c>
       <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4871,7 +5117,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>1711431582</v>
+        <v>1714233798</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -4885,6 +5131,7 @@
         </is>
       </c>
       <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4903,7 +5150,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>1711474241</v>
+        <v>1714240125</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -4917,6 +5164,7 @@
         </is>
       </c>
       <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4935,7 +5183,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>1711489011</v>
+        <v>1714249569</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -4949,6 +5197,11 @@
         </is>
       </c>
       <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4967,7 +5220,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>1711493686</v>
+        <v>1714267465</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -4981,6 +5234,7 @@
         </is>
       </c>
       <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4999,7 +5253,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>1711511494</v>
+        <v>1714274838</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -5013,6 +5267,7 @@
         </is>
       </c>
       <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5031,7 +5286,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>1711524510</v>
+        <v>1714284349</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -5045,6 +5300,7 @@
         </is>
       </c>
       <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5063,7 +5319,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>1711530124</v>
+        <v>1714290165</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -5077,198 +5333,7 @@
         </is>
       </c>
       <c r="H145" t="inlineStr"/>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Corridor</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>1711563188</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr"/>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>Corridor.Temperature.state: Cold</t>
-        </is>
-      </c>
-      <c r="H146" t="inlineStr"/>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Corridor</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>1711576882</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>Corridor.Temperature.state: ExcessivelyCold</t>
-        </is>
-      </c>
-      <c r="H147" t="inlineStr"/>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Corridor</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>1711581611</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>Corridor.Temperature.state: Cold</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr"/>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Corridor</t>
-        </is>
-      </c>
-      <c r="D149" t="n">
-        <v>1711598082</v>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr"/>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>Corridor.Temperature.state: Comfortable</t>
-        </is>
-      </c>
-      <c r="H149" t="inlineStr"/>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Corridor</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>1711611652</v>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>Corridor.Temperature.state: Warm</t>
-        </is>
-      </c>
-      <c r="H150" t="inlineStr"/>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Corridor</t>
-        </is>
-      </c>
-      <c r="D151" t="n">
-        <v>1711617577</v>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>Corridor.Temperature.state: Comfortable</t>
-        </is>
-      </c>
-      <c r="H151" t="inlineStr"/>
+      <c r="I145" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
